--- a/Result/profitability/3306.xlsx
+++ b/Result/profitability/3306.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.55</v>
       </c>
       <c r="M2" t="n">
-        <v>0.465</v>
+        <v>0.4175</v>
       </c>
       <c r="N2" t="n">
-        <v>27.29375</v>
+        <v>25.98</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.73</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4975</v>
+        <v>0.42875</v>
       </c>
       <c r="N3" t="n">
-        <v>24.975</v>
+        <v>23.5325</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.71</v>
       </c>
       <c r="M4" t="n">
-        <v>0.50625</v>
+        <v>0.53625</v>
       </c>
       <c r="N4" t="n">
-        <v>22.2925</v>
+        <v>21.74875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
         <v>97.3</v>
@@ -1018,10 +1018,10 @@
         <v>-0.61</v>
       </c>
       <c r="M5" t="n">
-        <v>0.44875</v>
+        <v>0.22875</v>
       </c>
       <c r="N5" t="n">
-        <v>19.8375</v>
+        <v>19.3375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.19</v>
       </c>
       <c r="M6" t="n">
-        <v>0.19375</v>
+        <v>0.19125</v>
       </c>
       <c r="N6" t="n">
-        <v>18.50875</v>
+        <v>18.59625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.37</v>
       </c>
       <c r="M7" t="n">
-        <v>0.22625</v>
+        <v>0.22</v>
       </c>
       <c r="N7" t="n">
-        <v>17.78</v>
+        <v>17.40125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.61</v>
       </c>
       <c r="M8" t="n">
-        <v>0.285</v>
+        <v>0.2825</v>
       </c>
       <c r="N8" t="n">
-        <v>16.61125</v>
+        <v>16.015</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3306</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>299</v>
+      </c>
+      <c r="D75" t="n">
+        <v>231</v>
+      </c>
+      <c r="E75" t="n">
+        <v>68</v>
+      </c>
+      <c r="F75" t="n">
+        <v>22.77</v>
+      </c>
+      <c r="G75" t="n">
+        <v>3</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.94%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>5</v>
+      </c>
+      <c r="K75" t="n">
+        <v>5</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.4075</v>
+      </c>
+      <c r="N75" t="n">
+        <v>27.4575</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1818181818181819</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-4.77</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1732026143790849</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-1.76</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.9513513513513514</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1494209936496078</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
